--- a/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
+++ b/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
@@ -1092,7 +1092,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1155,7 +1155,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1183,7 +1183,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1360,7 +1360,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1423,7 +1423,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1451,7 +1451,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M572"/>
+  <dimension ref="A1:M664"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18.6363636363636" customWidth="1" min="1" max="1"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1966,11 +1966,11 @@
         <v>114</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2023,11 +2023,11 @@
         <v>114</v>
       </c>
       <c r="H4" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2080,11 +2080,11 @@
         <v>114</v>
       </c>
       <c r="H5" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2137,11 +2137,11 @@
         <v>114</v>
       </c>
       <c r="H6" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2308,11 +2308,11 @@
         <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2365,11 +2365,11 @@
         <v>114</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2479,11 +2479,11 @@
         <v>114</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2593,11 +2593,11 @@
         <v>114</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2650,11 +2650,11 @@
         <v>114</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2764,11 +2764,11 @@
         <v>114</v>
       </c>
       <c r="H17" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2821,11 +2821,11 @@
         <v>114</v>
       </c>
       <c r="H18" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2878,11 +2878,11 @@
         <v>114</v>
       </c>
       <c r="H19" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2935,7 +2935,7 @@
         <v>114</v>
       </c>
       <c r="H20" t="n">
-        <v>136.8</v>
+        <v>306</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2992,11 +2992,11 @@
         <v>114</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>114</v>
       </c>
       <c r="H23" t="n">
-        <v>381.6</v>
+        <v>201.6</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3163,11 +3163,11 @@
         <v>114</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3220,7 +3220,7 @@
         <v>114</v>
       </c>
       <c r="H25" t="n">
-        <v>252</v>
+        <v>367.2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3334,11 +3334,11 @@
         <v>114</v>
       </c>
       <c r="H27" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3391,11 +3391,11 @@
         <v>114</v>
       </c>
       <c r="H28" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3505,11 +3505,11 @@
         <v>114</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>381.6</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3619,11 +3619,11 @@
         <v>114</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>151.2</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>114</v>
       </c>
       <c r="H33" t="n">
-        <v>201.6</v>
+        <v>136.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7118,98 +7118,5250 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>114</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L94">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>114</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L95">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>114</v>
+      </c>
+      <c r="H96" t="n">
+        <v>126</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L96">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>114</v>
+      </c>
+      <c r="H97" t="n">
+        <v>306</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L97">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GeshaSemi WashedRafael Velasco</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>114</v>
+      </c>
+      <c r="H98" t="n">
+        <v>144</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L98">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>114</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L99">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>114</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L100">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>114</v>
+      </c>
+      <c r="H101" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L101">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>114</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L102">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>114</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L103">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>114</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L104">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>114</v>
+      </c>
+      <c r="H105" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L105">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>114</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L106">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>114</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L107">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>114</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L108">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>114</v>
+      </c>
+      <c r="H109" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L109">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>114</v>
+      </c>
+      <c r="H110" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L110">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>114</v>
+      </c>
+      <c r="H111" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L111">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CastilloStrawberry WashedSanta Monica</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>114</v>
+      </c>
+      <c r="H112" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L112">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>114</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L113">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>114</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L114">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>114</v>
+      </c>
+      <c r="H115" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L115">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>114</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L116">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>114</v>
+      </c>
+      <c r="H117" t="n">
+        <v>252</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L117">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>114</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L118">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>114</v>
+      </c>
+      <c r="H119" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L119">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>114</v>
+      </c>
+      <c r="H120" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L120">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>114</v>
+      </c>
+      <c r="H121" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L121">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Hydrangea Drops</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>114</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L122">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>114</v>
+      </c>
+      <c r="H123" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L123">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Roaster's Choice Subscription</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L124">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>114</v>
+      </c>
+      <c r="H125" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L125">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026 Yessica Parra; El Mirador, Gesha - Colombia</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>250</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L126">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026 Albino Ibias; Tres Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>250</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L127">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 5th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>250</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L128">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026 Mery Garcito; Finca La Bendición - Ecuador</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>250</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L129">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026 Wilson Alba; Sierra Morena, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>250</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L130">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Yellow Gesha Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>250</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L131">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Sidra Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>250</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L132">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026 Bukeye; Musumba, Lot #1 - Burundi</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>250</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L133">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026 Jhon Saenz; Aromas De Aniz - Peru</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>250</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L134">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026 Samuel Aragon; Caminos Del Inka, Gesha - Peru</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>250</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L135">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026 Wilbert Almanza; Bella Rosa - Peru</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>250</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L136">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026 Diego Parra; La Hacienda, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>250</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L137">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026 Armando Hurtado; Los Pinos - Peru</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>250</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L138">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026 Ruvumu - Burundi</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>250</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L139">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026 Servio Botina; El Cedro - Colombia</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>250</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L140">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026 Samuel &amp; Mario Muriel; Los Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>250</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L141">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026 Perlitas - Colombia</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>250</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L142">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026 Ruarai; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>250</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L143">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026 Candelaria Santos; Tres De Mayo - Peru</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>250</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L144">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026 Umoco; Busambo Hill - Burundi</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>250</v>
+      </c>
+      <c r="H145" t="n">
+        <v>180</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L145">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026 David Berrio; Chiroso, New Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>250</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L146">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026 Genezard Perez; Vista Alegre - Peru</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>250</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L147">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026 Victor Dota - Ecuador</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>250</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L148">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026 Guchienda Estate; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>250</v>
+      </c>
+      <c r="H149" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L149">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 15th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>250</v>
+      </c>
+      <c r="H150" t="n">
+        <v>180</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L150">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026 Octavio Rueda; El Mirador, End Of Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>250</v>
+      </c>
+      <c r="H151" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L151">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026 Lisbeth Quispe; Yanacocha - Peru</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>250</v>
+      </c>
+      <c r="H152" t="n">
+        <v>216</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L152">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026 William Ortiz; La Cabaña, Chiroso - Colombia</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>250</v>
+      </c>
+      <c r="H153" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L153">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026 Juan Jose Huillca; Lot #Y-3 - Peru</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>250</v>
+      </c>
+      <c r="H154" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L154">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026 Vicente Regalado; La Capilla - Ecuador</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>250</v>
+      </c>
+      <c r="H155" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L155">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Calixto Quispe Mullisaca</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>150</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L156">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>150</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L157">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Moises Ccalla</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>150</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L158">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>150</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L159">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Nguisse Nare</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>150</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L160">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Bekele Kechara</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>150</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L161">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>150</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L162">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Duncan Lot 2004</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>150</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L163">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Finca El Espejo</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>150</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L164">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Chombi Plot</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>150</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L165">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Keramo</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>150</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L166">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Las Perlitas 3.0</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>150</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L167">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tuke Yute</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>150</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L168">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mariagracia Echeandia</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>150</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L169">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Finca Artemira</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>150</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L170">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Finca La Guaca</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>150</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L171">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>La Llanada</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>150</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L172">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>El Sol</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>150</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L173">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>150</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L174">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Aristóbulo Rayo</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>150</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L175">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Brayan Joven</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>150</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L176">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>150</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L177">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>La Concepcion</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>150</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L178">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Bochessa</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>150</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L179">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Marimira</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>150</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L180">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Pedro Garcia</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>150</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L181">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Fredesvinda Estela</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>150</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L182">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Hugo Gonzalez</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>150</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L183">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>German Ortiz</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>150</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L184">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Las Afiladeras</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>150</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L185">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
     <row r="186"/>
     <row r="187"/>
     <row r="188"/>
@@ -7593,21 +12745,113 @@
     <row r="566"/>
     <row r="567"/>
     <row r="568"/>
-    <row r="569">
-      <c r="A569" s="3" t="n"/>
-      <c r="C569" s="4" t="n"/>
-    </row>
-    <row r="570">
-      <c r="A570" s="3" t="n"/>
-      <c r="C570" s="4" t="n"/>
-    </row>
-    <row r="571">
-      <c r="A571" s="3" t="n"/>
-      <c r="C571" s="4" t="n"/>
-    </row>
-    <row r="572">
-      <c r="A572" s="3" t="n"/>
-      <c r="C572" s="4" t="n"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661">
+      <c r="A661" s="3" t="n"/>
+      <c r="C661" s="4" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="n"/>
+      <c r="C662" s="4" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="3" t="n"/>
+      <c r="C663" s="4" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="3" t="n"/>
+      <c r="C664" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
+++ b/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M664"/>
+  <dimension ref="A1:M756"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18.6363636363636" customWidth="1" min="1" max="1"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1966,11 +1966,11 @@
         <v>114</v>
       </c>
       <c r="H3" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2023,11 +2023,11 @@
         <v>114</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2365,11 +2365,11 @@
         <v>114</v>
       </c>
       <c r="H10" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2479,11 +2479,11 @@
         <v>114</v>
       </c>
       <c r="H12" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2536,11 +2536,11 @@
         <v>114</v>
       </c>
       <c r="H13" t="n">
-        <v>133.2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2593,11 +2593,11 @@
         <v>114</v>
       </c>
       <c r="H14" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2650,11 +2650,11 @@
         <v>114</v>
       </c>
       <c r="H15" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2935,11 +2935,11 @@
         <v>114</v>
       </c>
       <c r="H20" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2992,11 +2992,11 @@
         <v>114</v>
       </c>
       <c r="H21" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3106,11 +3106,11 @@
         <v>114</v>
       </c>
       <c r="H23" t="n">
-        <v>201.6</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3163,11 +3163,11 @@
         <v>114</v>
       </c>
       <c r="H24" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3220,11 +3220,11 @@
         <v>114</v>
       </c>
       <c r="H25" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3277,11 +3277,11 @@
         <v>114</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3448,11 +3448,11 @@
         <v>114</v>
       </c>
       <c r="H29" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3505,11 +3505,11 @@
         <v>114</v>
       </c>
       <c r="H30" t="n">
-        <v>381.6</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3562,11 +3562,11 @@
         <v>114</v>
       </c>
       <c r="H31" t="n">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3619,11 +3619,11 @@
         <v>114</v>
       </c>
       <c r="H32" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3676,11 +3676,11 @@
         <v>114</v>
       </c>
       <c r="H33" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7210,11 +7210,11 @@
         <v>114</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7267,11 +7267,11 @@
         <v>114</v>
       </c>
       <c r="H96" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7324,11 +7324,11 @@
         <v>114</v>
       </c>
       <c r="H97" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7381,11 +7381,11 @@
         <v>114</v>
       </c>
       <c r="H98" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7552,11 +7552,11 @@
         <v>114</v>
       </c>
       <c r="H101" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7609,11 +7609,11 @@
         <v>114</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7723,11 +7723,11 @@
         <v>114</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7837,11 +7837,11 @@
         <v>114</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7894,11 +7894,11 @@
         <v>114</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8008,11 +8008,11 @@
         <v>114</v>
       </c>
       <c r="H109" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8065,11 +8065,11 @@
         <v>114</v>
       </c>
       <c r="H110" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8122,11 +8122,11 @@
         <v>114</v>
       </c>
       <c r="H111" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8179,7 +8179,7 @@
         <v>114</v>
       </c>
       <c r="H112" t="n">
-        <v>136.8</v>
+        <v>306</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8236,11 +8236,11 @@
         <v>114</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8350,7 +8350,7 @@
         <v>114</v>
       </c>
       <c r="H115" t="n">
-        <v>381.6</v>
+        <v>201.6</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8407,11 +8407,11 @@
         <v>114</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8464,7 +8464,7 @@
         <v>114</v>
       </c>
       <c r="H117" t="n">
-        <v>252</v>
+        <v>367.2</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8578,11 +8578,11 @@
         <v>114</v>
       </c>
       <c r="H119" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8635,11 +8635,11 @@
         <v>114</v>
       </c>
       <c r="H120" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8749,11 +8749,11 @@
         <v>114</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>381.6</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8863,11 +8863,11 @@
         <v>114</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>151.2</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8920,7 +8920,7 @@
         <v>114</v>
       </c>
       <c r="H125" t="n">
-        <v>201.6</v>
+        <v>136.8</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -12362,98 +12362,5250 @@
         </is>
       </c>
     </row>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>114</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L186">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>114</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L187">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>114</v>
+      </c>
+      <c r="H188" t="n">
+        <v>126</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L188">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>114</v>
+      </c>
+      <c r="H189" t="n">
+        <v>306</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L189">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>GeshaSemi WashedRafael Velasco</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>114</v>
+      </c>
+      <c r="H190" t="n">
+        <v>144</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L190">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>114</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L191">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>114</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L192">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>114</v>
+      </c>
+      <c r="H193" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L193">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>114</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L194">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>114</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L195">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>114</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L196">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>114</v>
+      </c>
+      <c r="H197" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L197">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>114</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L198">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>114</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L199">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>114</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L200">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>114</v>
+      </c>
+      <c r="H201" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L201">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>114</v>
+      </c>
+      <c r="H202" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L202">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>114</v>
+      </c>
+      <c r="H203" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L203">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CastilloStrawberry WashedSanta Monica</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>114</v>
+      </c>
+      <c r="H204" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L204">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>114</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L205">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>114</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L206">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>114</v>
+      </c>
+      <c r="H207" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L207">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>114</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L208">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>114</v>
+      </c>
+      <c r="H209" t="n">
+        <v>252</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L209">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>114</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L210">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>114</v>
+      </c>
+      <c r="H211" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L211">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>114</v>
+      </c>
+      <c r="H212" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L212">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>114</v>
+      </c>
+      <c r="H213" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L213">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Hydrangea Drops</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>114</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L214">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>114</v>
+      </c>
+      <c r="H215" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L215">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Roaster's Choice Subscription</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>114</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L216">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>114</v>
+      </c>
+      <c r="H217" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L217">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026 Yessica Parra; El Mirador, Gesha - Colombia</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>250</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L218">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026 Albino Ibias; Tres Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>250</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L219">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 5th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>250</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L220">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026 Mery Garcito; Finca La Bendición - Ecuador</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>250</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L221">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026 Wilson Alba; Sierra Morena, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>250</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L222">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Yellow Gesha Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>250</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L223">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Sidra Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>250</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L224">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026 Bukeye; Musumba, Lot #1 - Burundi</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>250</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L225">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026 Jhon Saenz; Aromas De Aniz - Peru</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>250</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L226">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026 Samuel Aragon; Caminos Del Inka, Gesha - Peru</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>250</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L227">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026 Wilbert Almanza; Bella Rosa - Peru</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>250</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L228">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026 Diego Parra; La Hacienda, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>250</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L229">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026 Armando Hurtado; Los Pinos - Peru</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>250</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L230">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026 Ruvumu - Burundi</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>250</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L231">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026 Servio Botina; El Cedro - Colombia</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>250</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L232">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026 Samuel &amp; Mario Muriel; Los Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>250</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L233">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026 Perlitas - Colombia</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>250</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L234">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026 Ruarai; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>250</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L235">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026 Candelaria Santos; Tres De Mayo - Peru</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>250</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L236">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026 Umoco; Busambo Hill - Burundi</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>250</v>
+      </c>
+      <c r="H237" t="n">
+        <v>180</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L237">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026 David Berrio; Chiroso, New Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>250</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L238">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026 Genezard Perez; Vista Alegre - Peru</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>250</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L239">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026 Victor Dota - Ecuador</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>250</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L240">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026 Guchienda Estate; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>250</v>
+      </c>
+      <c r="H241" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L241">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 15th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>250</v>
+      </c>
+      <c r="H242" t="n">
+        <v>180</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L242">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026 Octavio Rueda; El Mirador, End Of Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>250</v>
+      </c>
+      <c r="H243" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L243">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026 Lisbeth Quispe; Yanacocha - Peru</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>250</v>
+      </c>
+      <c r="H244" t="n">
+        <v>216</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L244">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026 William Ortiz; La Cabaña, Chiroso - Colombia</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>250</v>
+      </c>
+      <c r="H245" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L245">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026 Juan Jose Huillca; Lot #Y-3 - Peru</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>250</v>
+      </c>
+      <c r="H246" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L246">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026 Vicente Regalado; La Capilla - Ecuador</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>250</v>
+      </c>
+      <c r="H247" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L247">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Calixto Quispe Mullisaca</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>150</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L248">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>150</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L249">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Moises Ccalla</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>150</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L250">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>150</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L251">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Nguisse Nare</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>150</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L252">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Bekele Kechara</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>150</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L253">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>150</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L254">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Duncan Lot 2004</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>150</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L255">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Finca El Espejo</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>150</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L256">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Chombi Plot</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>150</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L257">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Keramo</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>150</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L258">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Las Perlitas 3.0</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>150</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L259">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Tuke Yute</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>150</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L260">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Mariagracia Echeandia</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>150</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L261">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Finca Artemira</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>150</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L262">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Finca La Guaca</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>150</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L263">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>La Llanada</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>150</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L264">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>El Sol</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>150</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L265">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>150</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L266">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Aristóbulo Rayo</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>150</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L267">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Brayan Joven</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>150</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L268">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>150</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L269">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>La Concepcion</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>150</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L270">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Bochessa</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>150</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L271">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Marimira</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>150</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L272">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Pedro Garcia</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>150</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L273">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Fredesvinda Estela</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>150</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L274">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Hugo Gonzalez</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>150</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L275">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>German Ortiz</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>150</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L276">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Las Afiladeras</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>150</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L277">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
     <row r="278"/>
     <row r="279"/>
     <row r="280"/>
@@ -12837,21 +17989,113 @@
     <row r="658"/>
     <row r="659"/>
     <row r="660"/>
-    <row r="661">
-      <c r="A661" s="3" t="n"/>
-      <c r="C661" s="4" t="n"/>
-    </row>
-    <row r="662">
-      <c r="A662" s="3" t="n"/>
-      <c r="C662" s="4" t="n"/>
-    </row>
-    <row r="663">
-      <c r="A663" s="3" t="n"/>
-      <c r="C663" s="4" t="n"/>
-    </row>
-    <row r="664">
-      <c r="A664" s="3" t="n"/>
-      <c r="C664" s="4" t="n"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753">
+      <c r="A753" s="3" t="n"/>
+      <c r="C753" s="4" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="3" t="n"/>
+      <c r="C754" s="4" t="n"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="n"/>
+      <c r="C755" s="4" t="n"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="3" t="n"/>
+      <c r="C756" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
+++ b/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M756"/>
+  <dimension ref="A1:M848"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18.6363636363636" customWidth="1" min="1" max="1"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2023,11 +2023,11 @@
         <v>114</v>
       </c>
       <c r="H4" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2308,11 +2308,11 @@
         <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3277,11 +3277,11 @@
         <v>114</v>
       </c>
       <c r="H26" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3334,11 +3334,11 @@
         <v>114</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7210,11 +7210,11 @@
         <v>114</v>
       </c>
       <c r="H95" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7267,11 +7267,11 @@
         <v>114</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7609,11 +7609,11 @@
         <v>114</v>
       </c>
       <c r="H102" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7723,11 +7723,11 @@
         <v>114</v>
       </c>
       <c r="H104" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7780,11 +7780,11 @@
         <v>114</v>
       </c>
       <c r="H105" t="n">
-        <v>133.2</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7837,11 +7837,11 @@
         <v>114</v>
       </c>
       <c r="H106" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7894,11 +7894,11 @@
         <v>114</v>
       </c>
       <c r="H107" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8179,11 +8179,11 @@
         <v>114</v>
       </c>
       <c r="H112" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8236,11 +8236,11 @@
         <v>114</v>
       </c>
       <c r="H113" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8350,11 +8350,11 @@
         <v>114</v>
       </c>
       <c r="H115" t="n">
-        <v>201.6</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8407,11 +8407,11 @@
         <v>114</v>
       </c>
       <c r="H116" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8464,11 +8464,11 @@
         <v>114</v>
       </c>
       <c r="H117" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8521,11 +8521,11 @@
         <v>114</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8692,11 +8692,11 @@
         <v>114</v>
       </c>
       <c r="H121" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8749,11 +8749,11 @@
         <v>114</v>
       </c>
       <c r="H122" t="n">
-        <v>381.6</v>
+        <v>0</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8806,11 +8806,11 @@
         <v>114</v>
       </c>
       <c r="H123" t="n">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8863,11 +8863,11 @@
         <v>114</v>
       </c>
       <c r="H124" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8920,11 +8920,11 @@
         <v>114</v>
       </c>
       <c r="H125" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12454,11 +12454,11 @@
         <v>114</v>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12511,11 +12511,11 @@
         <v>114</v>
       </c>
       <c r="H188" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12568,11 +12568,11 @@
         <v>114</v>
       </c>
       <c r="H189" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12625,11 +12625,11 @@
         <v>114</v>
       </c>
       <c r="H190" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12796,11 +12796,11 @@
         <v>114</v>
       </c>
       <c r="H193" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12853,11 +12853,11 @@
         <v>114</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12967,11 +12967,11 @@
         <v>114</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -13081,11 +13081,11 @@
         <v>114</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13138,11 +13138,11 @@
         <v>114</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13252,11 +13252,11 @@
         <v>114</v>
       </c>
       <c r="H201" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13309,11 +13309,11 @@
         <v>114</v>
       </c>
       <c r="H202" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13366,11 +13366,11 @@
         <v>114</v>
       </c>
       <c r="H203" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13423,7 +13423,7 @@
         <v>114</v>
       </c>
       <c r="H204" t="n">
-        <v>136.8</v>
+        <v>306</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13480,11 +13480,11 @@
         <v>114</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13594,7 +13594,7 @@
         <v>114</v>
       </c>
       <c r="H207" t="n">
-        <v>381.6</v>
+        <v>201.6</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13651,11 +13651,11 @@
         <v>114</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13708,7 +13708,7 @@
         <v>114</v>
       </c>
       <c r="H209" t="n">
-        <v>252</v>
+        <v>367.2</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13822,11 +13822,11 @@
         <v>114</v>
       </c>
       <c r="H211" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13879,11 +13879,11 @@
         <v>114</v>
       </c>
       <c r="H212" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13993,11 +13993,11 @@
         <v>114</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>381.6</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -14107,11 +14107,11 @@
         <v>114</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>151.2</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14164,7 +14164,7 @@
         <v>114</v>
       </c>
       <c r="H217" t="n">
-        <v>201.6</v>
+        <v>136.8</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -17606,98 +17606,5250 @@
         </is>
       </c>
     </row>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>114</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L278">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>114</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L279">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>114</v>
+      </c>
+      <c r="H280" t="n">
+        <v>126</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L280">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>114</v>
+      </c>
+      <c r="H281" t="n">
+        <v>306</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L281">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>GeshaSemi WashedRafael Velasco</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>114</v>
+      </c>
+      <c r="H282" t="n">
+        <v>144</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L282">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>114</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L283">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>114</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L284">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>114</v>
+      </c>
+      <c r="H285" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L285">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>114</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L286">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>114</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L287">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>114</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L288">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>114</v>
+      </c>
+      <c r="H289" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L289">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>114</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L290">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>114</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L291">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>114</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L292">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>114</v>
+      </c>
+      <c r="H293" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L293">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>114</v>
+      </c>
+      <c r="H294" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L294">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>114</v>
+      </c>
+      <c r="H295" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L295">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>CastilloStrawberry WashedSanta Monica</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>114</v>
+      </c>
+      <c r="H296" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L296">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>114</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L297">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>114</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L298">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>114</v>
+      </c>
+      <c r="H299" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L299">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>114</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L300">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>114</v>
+      </c>
+      <c r="H301" t="n">
+        <v>252</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L301">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>114</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L302">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>114</v>
+      </c>
+      <c r="H303" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L303">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>114</v>
+      </c>
+      <c r="H304" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L304">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>114</v>
+      </c>
+      <c r="H305" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L305">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Hydrangea Drops</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>114</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L306">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>114</v>
+      </c>
+      <c r="H307" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L307">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Roaster's Choice Subscription</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>114</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L308">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>114</v>
+      </c>
+      <c r="H309" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L309">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026 Yessica Parra; El Mirador, Gesha - Colombia</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>250</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L310">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026 Albino Ibias; Tres Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>250</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L311">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 5th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>250</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L312">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026 Mery Garcito; Finca La Bendición - Ecuador</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>250</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L313">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026 Wilson Alba; Sierra Morena, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>250</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L314">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Yellow Gesha Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>250</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L315">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Sidra Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>250</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L316">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026 Bukeye; Musumba, Lot #1 - Burundi</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>250</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L317">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026 Jhon Saenz; Aromas De Aniz - Peru</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>250</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L318">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026 Samuel Aragon; Caminos Del Inka, Gesha - Peru</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>250</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L319">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026 Wilbert Almanza; Bella Rosa - Peru</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>250</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L320">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026 Diego Parra; La Hacienda, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>250</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L321">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026 Armando Hurtado; Los Pinos - Peru</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>250</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L322">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026 Ruvumu - Burundi</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>250</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L323">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026 Servio Botina; El Cedro - Colombia</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>250</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L324">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026 Samuel &amp; Mario Muriel; Los Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>250</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L325">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026 Perlitas - Colombia</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>250</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L326">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026 Ruarai; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>250</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L327">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026 Candelaria Santos; Tres De Mayo - Peru</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>250</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L328">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026 Umoco; Busambo Hill - Burundi</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>250</v>
+      </c>
+      <c r="H329" t="n">
+        <v>180</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L329">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026 David Berrio; Chiroso, New Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>250</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L330">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026 Genezard Perez; Vista Alegre - Peru</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>250</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L331">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026 Victor Dota - Ecuador</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>250</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L332">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026 Guchienda Estate; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>250</v>
+      </c>
+      <c r="H333" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L333">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 15th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>250</v>
+      </c>
+      <c r="H334" t="n">
+        <v>180</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L334">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026 Octavio Rueda; El Mirador, End Of Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>250</v>
+      </c>
+      <c r="H335" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L335">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026 Lisbeth Quispe; Yanacocha - Peru</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>250</v>
+      </c>
+      <c r="H336" t="n">
+        <v>216</v>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L336">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026 William Ortiz; La Cabaña, Chiroso - Colombia</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>250</v>
+      </c>
+      <c r="H337" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L337">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026 Juan Jose Huillca; Lot #Y-3 - Peru</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>250</v>
+      </c>
+      <c r="H338" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L338">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026 Vicente Regalado; La Capilla - Ecuador</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>250</v>
+      </c>
+      <c r="H339" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L339">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Calixto Quispe Mullisaca</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>150</v>
+      </c>
+      <c r="H340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L340">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>150</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L341">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Moises Ccalla</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>150</v>
+      </c>
+      <c r="H342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L342">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>150</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L343">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Nguisse Nare</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>150</v>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L344">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Bekele Kechara</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>150</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L345">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>150</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L346">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Duncan Lot 2004</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>150</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L347">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Finca El Espejo</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>150</v>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L348">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Chombi Plot</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>150</v>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L349">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Keramo</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>150</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L350">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Las Perlitas 3.0</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>150</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L351">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Tuke Yute</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>150</v>
+      </c>
+      <c r="H352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L352">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Mariagracia Echeandia</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>150</v>
+      </c>
+      <c r="H353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L353">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Finca Artemira</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>150</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L354">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Finca La Guaca</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>150</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L355">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>La Llanada</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>150</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L356">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>El Sol</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>150</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L357">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>150</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L358">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Aristóbulo Rayo</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>150</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L359">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Brayan Joven</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>150</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L360">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>150</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L361">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>La Concepcion</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>150</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L362">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Bochessa</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>150</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L363">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Marimira</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>150</v>
+      </c>
+      <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L364">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Pedro Garcia</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>150</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L365">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Fredesvinda Estela</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>150</v>
+      </c>
+      <c r="H366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L366">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Hugo Gonzalez</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>150</v>
+      </c>
+      <c r="H367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L367">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>German Ortiz</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>150</v>
+      </c>
+      <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L368">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Las Afiladeras</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>150</v>
+      </c>
+      <c r="H369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L369">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
     <row r="370"/>
     <row r="371"/>
     <row r="372"/>
@@ -18081,21 +23233,113 @@
     <row r="750"/>
     <row r="751"/>
     <row r="752"/>
-    <row r="753">
-      <c r="A753" s="3" t="n"/>
-      <c r="C753" s="4" t="n"/>
-    </row>
-    <row r="754">
-      <c r="A754" s="3" t="n"/>
-      <c r="C754" s="4" t="n"/>
-    </row>
-    <row r="755">
-      <c r="A755" s="3" t="n"/>
-      <c r="C755" s="4" t="n"/>
-    </row>
-    <row r="756">
-      <c r="A756" s="3" t="n"/>
-      <c r="C756" s="4" t="n"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845">
+      <c r="A845" s="3" t="n"/>
+      <c r="C845" s="4" t="n"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="3" t="n"/>
+      <c r="C846" s="4" t="n"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="3" t="n"/>
+      <c r="C847" s="4" t="n"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="3" t="n"/>
+      <c r="C848" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
+++ b/Specialty_Coffee_Market_Radar_3.1_RMB.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M848"/>
+  <dimension ref="A1:M940"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18.6363636363636" customWidth="1" min="1" max="1"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1909,11 +1909,11 @@
         <v>114</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2308,11 +2308,11 @@
         <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3163,11 +3163,11 @@
         <v>114</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3334,11 +3334,11 @@
         <v>114</v>
       </c>
       <c r="H27" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7267,11 +7267,11 @@
         <v>114</v>
       </c>
       <c r="H96" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7552,11 +7552,11 @@
         <v>114</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8521,11 +8521,11 @@
         <v>114</v>
       </c>
       <c r="H118" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8578,11 +8578,11 @@
         <v>114</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12454,11 +12454,11 @@
         <v>114</v>
       </c>
       <c r="H187" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12511,11 +12511,11 @@
         <v>114</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12853,11 +12853,11 @@
         <v>114</v>
       </c>
       <c r="H194" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12967,11 +12967,11 @@
         <v>114</v>
       </c>
       <c r="H196" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -13024,11 +13024,11 @@
         <v>114</v>
       </c>
       <c r="H197" t="n">
-        <v>133.2</v>
+        <v>0</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -13081,11 +13081,11 @@
         <v>114</v>
       </c>
       <c r="H198" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13138,11 +13138,11 @@
         <v>114</v>
       </c>
       <c r="H199" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13423,11 +13423,11 @@
         <v>114</v>
       </c>
       <c r="H204" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13480,11 +13480,11 @@
         <v>114</v>
       </c>
       <c r="H205" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13594,11 +13594,11 @@
         <v>114</v>
       </c>
       <c r="H207" t="n">
-        <v>201.6</v>
+        <v>0</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13651,11 +13651,11 @@
         <v>114</v>
       </c>
       <c r="H208" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13708,11 +13708,11 @@
         <v>114</v>
       </c>
       <c r="H209" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13765,11 +13765,11 @@
         <v>114</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13936,11 +13936,11 @@
         <v>114</v>
       </c>
       <c r="H213" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13993,11 +13993,11 @@
         <v>114</v>
       </c>
       <c r="H214" t="n">
-        <v>381.6</v>
+        <v>0</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -14050,11 +14050,11 @@
         <v>114</v>
       </c>
       <c r="H215" t="n">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -14107,11 +14107,11 @@
         <v>114</v>
       </c>
       <c r="H216" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14164,11 +14164,11 @@
         <v>114</v>
       </c>
       <c r="H217" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+          <t>GeshaSemi WashedRafael Velasco</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -17698,11 +17698,11 @@
         <v>114</v>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>CastilloLycheeFinca El Paraiso</t>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -17755,11 +17755,11 @@
         <v>114</v>
       </c>
       <c r="H280" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -17812,11 +17812,11 @@
         <v>114</v>
       </c>
       <c r="H281" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>GeshaSemi WashedRafael Velasco</t>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -17869,11 +17869,11 @@
         <v>114</v>
       </c>
       <c r="H282" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18040,11 +18040,11 @@
         <v>114</v>
       </c>
       <c r="H285" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -18097,11 +18097,11 @@
         <v>114</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>San JuanXO NaturalFinca Potosi</t>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -18211,11 +18211,11 @@
         <v>114</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>136.8</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18325,11 +18325,11 @@
         <v>114</v>
       </c>
       <c r="H290" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -18382,11 +18382,11 @@
         <v>114</v>
       </c>
       <c r="H291" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+          <t>San JuanXO NaturalFinca Potosi</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -18496,11 +18496,11 @@
         <v>114</v>
       </c>
       <c r="H293" t="n">
-        <v>367.2</v>
+        <v>0</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -18553,11 +18553,11 @@
         <v>114</v>
       </c>
       <c r="H294" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -18610,11 +18610,11 @@
         <v>114</v>
       </c>
       <c r="H295" t="n">
-        <v>136.8</v>
+        <v>0</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>CastilloStrawberry WashedSanta Monica</t>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -18667,7 +18667,7 @@
         <v>114</v>
       </c>
       <c r="H296" t="n">
-        <v>136.8</v>
+        <v>306</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -18724,11 +18724,11 @@
         <v>114</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -18838,7 +18838,7 @@
         <v>114</v>
       </c>
       <c r="H299" t="n">
-        <v>381.6</v>
+        <v>201.6</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+          <t>CastilloLycheeFinca El Paraiso</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -18895,11 +18895,11 @@
         <v>114</v>
       </c>
       <c r="H300" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -18935,7 +18935,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>[Rested] GeshaNatural Lot 909Janson</t>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -18952,7 +18952,7 @@
         <v>114</v>
       </c>
       <c r="H301" t="n">
-        <v>252</v>
+        <v>367.2</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+          <t>Roaster's Choice Subscription</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -19066,11 +19066,11 @@
         <v>114</v>
       </c>
       <c r="H303" t="n">
-        <v>129.6</v>
+        <v>0</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+          <t>Hydrangea Drops</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -19123,11 +19123,11 @@
         <v>114</v>
       </c>
       <c r="H304" t="n">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -19163,7 +19163,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+          <t>CastilloStrawberry WashedSanta Monica</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Hydrangea Drops</t>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -19237,11 +19237,11 @@
         <v>114</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>381.6</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Roaster's Choice Subscription</t>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -19351,11 +19351,11 @@
         <v>114</v>
       </c>
       <c r="H308" t="n">
-        <v>0</v>
+        <v>151.2</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>GeshaSalma BermudezFinca El Paraiso</t>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -19408,7 +19408,7 @@
         <v>114</v>
       </c>
       <c r="H309" t="n">
-        <v>201.6</v>
+        <v>136.8</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -22850,98 +22850,5250 @@
         </is>
       </c>
     </row>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>114</v>
+      </c>
+      <c r="H370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L370">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural ASD T2DElida Estate, Lot Plano</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>114</v>
+      </c>
+      <c r="H371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L371">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CastilloLycheeFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>114</v>
+      </c>
+      <c r="H372" t="n">
+        <v>126</v>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L372">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashed DRDEl Burro Lot 16</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>114</v>
+      </c>
+      <c r="H373" t="n">
+        <v>306</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L373">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>GeshaSemi WashedRafael Velasco</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>114</v>
+      </c>
+      <c r="H374" t="n">
+        <v>144</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L374">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>[Rested] San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>114</v>
+      </c>
+      <c r="H375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L375">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceAnaerobic NaturalMelese Wolde</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>114</v>
+      </c>
+      <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L376">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Typica MejoradoNaturalHacienda La Papaya, Yunguilla Farm</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>114</v>
+      </c>
+      <c r="H377" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L377">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>[Rested] Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>114</v>
+      </c>
+      <c r="H378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L378">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>San JuanXO NaturalFinca Potosi</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>114</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L379">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 15El Burro</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>114</v>
+      </c>
+      <c r="H380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L380">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Typica MejoradoYeast Inoculated WashedHacienda La Papaya, Yacuri Farm</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>114</v>
+      </c>
+      <c r="H381" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L381">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaWashedFinca Mi Finquita, Lot E</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>114</v>
+      </c>
+      <c r="H382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L382">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural El VeloHacienda La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>114</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L383">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>114</v>
+      </c>
+      <c r="H384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L384">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>GeshaWashedAbu Coffee, GW‑3210</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>114</v>
+      </c>
+      <c r="H385" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L385">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>114</v>
+      </c>
+      <c r="H386" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L386">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>114</v>
+      </c>
+      <c r="H387" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L387">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CastilloStrawberry WashedSanta Monica</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>114</v>
+      </c>
+      <c r="H388" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L388">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>[Rested] CastilloThermal Shock DecafFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>114</v>
+      </c>
+      <c r="H389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L389">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>[Rested] Caturra, BourbonNectar Citrullus WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>114</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L390">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>GeshaNaturalAbu Coffee, GN‑3170</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>114</v>
+      </c>
+      <c r="H391" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L391">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>[Rested] LandraceWashedTagel Alemayehu</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>114</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L392">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>[Rested] GeshaNatural Lot 909Janson</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>114</v>
+      </c>
+      <c r="H393" t="n">
+        <v>252</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L393">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>[Rested] Typica MejoradoWashedHacienda La Papaya</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>114</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L394">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>LandraceWashedHabtamu Fekadu Aga, Chelbesa Outgrowers</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>114</v>
+      </c>
+      <c r="H395" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L395">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Pink Bourbon + GeshaWashedFinca Los Capachos</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>114</v>
+      </c>
+      <c r="H396" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L396">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Purple CaturraMora Azul WashedMonteblanco</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>114</v>
+      </c>
+      <c r="H397" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L397">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Hydrangea Drops</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>114</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L398">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>GeshaLetty BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>114</v>
+      </c>
+      <c r="H399" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L399">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Roaster's Choice Subscription</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>114</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L400">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Hydrangea Coffee</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>GeshaSalma BermudezFinca El Paraiso</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>114</v>
+      </c>
+      <c r="H401" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L401">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026 Yessica Parra; El Mirador, Gesha - Colombia</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>250</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L402">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026 Albino Ibias; Tres Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>250</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L403">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 5th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>250</v>
+      </c>
+      <c r="H404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L404">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026 Mery Garcito; Finca La Bendición - Ecuador</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>250</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L405">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026 Wilson Alba; Sierra Morena, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>250</v>
+      </c>
+      <c r="H406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L406">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Yellow Gesha Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>250</v>
+      </c>
+      <c r="H407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L407">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026 Neto; La Margarita, Sidra Reserve Lot - Peru</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>250</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L408">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026 Bukeye; Musumba, Lot #1 - Burundi</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>250</v>
+      </c>
+      <c r="H409" t="n">
+        <v>0</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L409">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026 Jhon Saenz; Aromas De Aniz - Peru</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>250</v>
+      </c>
+      <c r="H410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L410">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026 Samuel Aragon; Caminos Del Inka, Gesha - Peru</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>250</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L411">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026 Wilbert Almanza; Bella Rosa - Peru</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>250</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L412">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026 Diego Parra; La Hacienda, 2nd Harvest - Colombia</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>250</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L413">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026 Armando Hurtado; Los Pinos - Peru</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>250</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L414">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026 Ruvumu - Burundi</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>250</v>
+      </c>
+      <c r="H415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L415">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026 Servio Botina; El Cedro - Colombia</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>250</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L416">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026 Samuel &amp; Mario Muriel; Los Cedros - Peru</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>250</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L417">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026 Perlitas - Colombia</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>250</v>
+      </c>
+      <c r="H418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L418">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026 Ruarai; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>250</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L419">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026 Candelaria Santos; Tres De Mayo - Peru</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>250</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L420">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026 Umoco; Busambo Hill - Burundi</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>250</v>
+      </c>
+      <c r="H421" t="n">
+        <v>180</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L421">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026 David Berrio; Chiroso, New Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>250</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L422">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026 Genezard Perez; Vista Alegre - Peru</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>250</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L423">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026 Victor Dota - Ecuador</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>250</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L424">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026 Guchienda Estate; AA Separation - Kenya</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>250</v>
+      </c>
+      <c r="H425" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L425">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026 Ninga; Bumba Hill, May 15th Harvest - Burundi</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>250</v>
+      </c>
+      <c r="H426" t="n">
+        <v>180</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L426">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026 Octavio Rueda; El Mirador, End Of Season - Colombia</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>250</v>
+      </c>
+      <c r="H427" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L427">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026 Lisbeth Quispe; Yanacocha - Peru</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>250</v>
+      </c>
+      <c r="H428" t="n">
+        <v>216</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L428">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026 William Ortiz; La Cabaña, Chiroso - Colombia</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>250</v>
+      </c>
+      <c r="H429" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L429">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026 Juan Jose Huillca; Lot #Y-3 - Peru</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>250</v>
+      </c>
+      <c r="H430" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L430">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Sey Coffee</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026 Vicente Regalado; La Capilla - Ecuador</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>250</v>
+      </c>
+      <c r="H431" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L431">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Calixto Quispe Mullisaca</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>150</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L432">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>150</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L433">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Moises Ccalla</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>150</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L434">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>150</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L435">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Nguisse Nare</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>150</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L436">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Bekele Kechara</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>150</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L437">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Mate Matiwos</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>150</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L438">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Duncan Lot 2004</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>150</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L439">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Finca El Espejo</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>150</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L440">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Chombi Plot</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>150</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L441">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Keramo</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>150</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L442">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Las Perlitas 3.0</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>150</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L443">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Tuke Yute</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>150</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L444">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Mariagracia Echeandia</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>150</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L445">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Finca Artemira</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>150</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L446">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Finca La Guaca</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>150</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L447">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>La Llanada</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>150</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L448">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>El Sol</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>150</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L449">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>150</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L450">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Aristóbulo Rayo</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>150</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L451">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Brayan Joven</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>150</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L452">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>La Esmeralda</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>150</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L453">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>La Concepcion</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>150</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L454">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Bochessa</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>150</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L455">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Marimira</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>150</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L456">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Pedro Garcia</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>150</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L457">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Fredesvinda Estela</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>150</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L458">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Hugo Gonzalez</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>150</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L459">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>German Ortiz</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>150</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L460">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Botz Coffee</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Las Afiladeras</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>150</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L461">
+        <f>H2/G2</f>
+        <v/>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
     <row r="462"/>
     <row r="463"/>
     <row r="464"/>
@@ -23325,21 +28477,113 @@
     <row r="842"/>
     <row r="843"/>
     <row r="844"/>
-    <row r="845">
-      <c r="A845" s="3" t="n"/>
-      <c r="C845" s="4" t="n"/>
-    </row>
-    <row r="846">
-      <c r="A846" s="3" t="n"/>
-      <c r="C846" s="4" t="n"/>
-    </row>
-    <row r="847">
-      <c r="A847" s="3" t="n"/>
-      <c r="C847" s="4" t="n"/>
-    </row>
-    <row r="848">
-      <c r="A848" s="3" t="n"/>
-      <c r="C848" s="4" t="n"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937">
+      <c r="A937" s="3" t="n"/>
+      <c r="C937" s="4" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="3" t="n"/>
+      <c r="C938" s="4" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="3" t="n"/>
+      <c r="C939" s="4" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="3" t="n"/>
+      <c r="C940" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
